--- a/source_data.xlsx
+++ b/source_data.xlsx
@@ -6,17 +6,24 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Figure_2" r:id="rId3" sheetId="1"/>
-    <sheet name="Figure_3A" r:id="rId4" sheetId="2"/>
-    <sheet name="Figure_3B" r:id="rId5" sheetId="3"/>
-    <sheet name="Figure_3C" r:id="rId6" sheetId="4"/>
-    <sheet name="Figure_3D" r:id="rId7" sheetId="5"/>
+    <sheet name="2" r:id="rId3" sheetId="1"/>
+    <sheet name="3A" r:id="rId4" sheetId="2"/>
+    <sheet name="3B" r:id="rId5" sheetId="3"/>
+    <sheet name="3C" r:id="rId6" sheetId="4"/>
+    <sheet name="3D" r:id="rId7" sheetId="5"/>
+    <sheet name="4A" r:id="rId8" sheetId="6"/>
+    <sheet name="4B" r:id="rId9" sheetId="7"/>
+    <sheet name="5A" r:id="rId10" sheetId="8"/>
+    <sheet name="5B" r:id="rId11" sheetId="9"/>
+    <sheet name="5C" r:id="rId12" sheetId="10"/>
+    <sheet name="5D" r:id="rId13" sheetId="11"/>
+    <sheet name="5F" r:id="rId14" sheetId="12"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1179" uniqueCount="690">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1747" uniqueCount="767">
   <si>
     <t>strains.ID_strains</t>
   </si>
@@ -2086,6 +2093,237 @@
   </si>
   <si>
     <t>RS_GCF_000007185.1.Zc</t>
+  </si>
+  <si>
+    <t>OSCODE</t>
+  </si>
+  <si>
+    <t>Cellular_organisms</t>
+  </si>
+  <si>
+    <t>Euk_Archaea</t>
+  </si>
+  <si>
+    <t>Eukaryota</t>
+  </si>
+  <si>
+    <t>Opisthokonta</t>
+  </si>
+  <si>
+    <t>Eumetazoa</t>
+  </si>
+  <si>
+    <t>Vertebrata</t>
+  </si>
+  <si>
+    <t>Mammalia</t>
+  </si>
+  <si>
+    <t>PANTR</t>
+  </si>
+  <si>
+    <t>MACMU</t>
+  </si>
+  <si>
+    <t>MONDO</t>
+  </si>
+  <si>
+    <t>ORNAN</t>
+  </si>
+  <si>
+    <t>HUMAN</t>
+  </si>
+  <si>
+    <t>MOUSE</t>
+  </si>
+  <si>
+    <t>RAT</t>
+  </si>
+  <si>
+    <t>CANLF</t>
+  </si>
+  <si>
+    <t>BOVIN</t>
+  </si>
+  <si>
+    <t>Dikarya</t>
+  </si>
+  <si>
+    <t>Ascomycota</t>
+  </si>
+  <si>
+    <t>Saccharomyceta</t>
+  </si>
+  <si>
+    <t>SCLS1</t>
+  </si>
+  <si>
+    <t>NEUCR</t>
+  </si>
+  <si>
+    <t>YARLI</t>
+  </si>
+  <si>
+    <t>CANAL</t>
+  </si>
+  <si>
+    <t>YEAST</t>
+  </si>
+  <si>
+    <t>PHANO</t>
+  </si>
+  <si>
+    <t>protein</t>
+  </si>
+  <si>
+    <t>aa_subs</t>
+  </si>
+  <si>
+    <t>age</t>
+  </si>
+  <si>
+    <t>I/II/III</t>
+  </si>
+  <si>
+    <t>I/III</t>
+  </si>
+  <si>
+    <t>I/III'</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>IA/B</t>
+  </si>
+  <si>
+    <t>IB</t>
+  </si>
+  <si>
+    <t>node</t>
+  </si>
+  <si>
+    <t>Zc_D</t>
+  </si>
+  <si>
+    <t>Zc_K</t>
+  </si>
+  <si>
+    <t>Zc_H</t>
+  </si>
+  <si>
+    <t>1206_map</t>
+  </si>
+  <si>
+    <t>1207_map</t>
+  </si>
+  <si>
+    <t>Anc4_1223</t>
+  </si>
+  <si>
+    <t>Anc3_1231</t>
+  </si>
+  <si>
+    <t>Anc2_1304</t>
+  </si>
+  <si>
+    <t>Anc1_1312</t>
+  </si>
+  <si>
+    <t>WT_Nif_Azotobacter_vinelandii</t>
+  </si>
+  <si>
+    <t>lineage</t>
+  </si>
+  <si>
+    <t>age_min</t>
+  </si>
+  <si>
+    <t>age_max</t>
+  </si>
+  <si>
+    <t>Bacteria</t>
+  </si>
+  <si>
+    <t>Arc-Euk</t>
+  </si>
+  <si>
+    <t>LBCA</t>
+  </si>
+  <si>
+    <t>LPBCA</t>
+  </si>
+  <si>
+    <t>LGPCA</t>
+  </si>
+  <si>
+    <t>Ecoli</t>
+  </si>
+  <si>
+    <t>AECA</t>
+  </si>
+  <si>
+    <t>LACA</t>
+  </si>
+  <si>
+    <t>LECA</t>
+  </si>
+  <si>
+    <t>LAFCA</t>
+  </si>
+  <si>
+    <t>Human</t>
+  </si>
+  <si>
+    <t>Anc01</t>
+  </si>
+  <si>
+    <t>Anc02</t>
+  </si>
+  <si>
+    <t>Anc03</t>
+  </si>
+  <si>
+    <t>Anc04</t>
+  </si>
+  <si>
+    <t>Anc05</t>
+  </si>
+  <si>
+    <t>Anc06</t>
+  </si>
+  <si>
+    <t>Anc07</t>
+  </si>
+  <si>
+    <t>Anc08</t>
+  </si>
+  <si>
+    <t>Anc09</t>
+  </si>
+  <si>
+    <t>Anc10</t>
+  </si>
+  <si>
+    <t>Anc11</t>
+  </si>
+  <si>
+    <t>EcIPMDH</t>
+  </si>
+  <si>
+    <t>source</t>
+  </si>
+  <si>
+    <t>Age_Ga</t>
+  </si>
+  <si>
+    <t>T_C</t>
+  </si>
+  <si>
+    <t>Isson and Rauzi (2024)</t>
+  </si>
+  <si>
+    <t>Jaffrés et al. (2007)</t>
   </si>
 </sst>
 </file>
@@ -8716,6 +8954,5638 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>736</v>
+      </c>
+      <c r="B1" t="s">
+        <v>716</v>
+      </c>
+      <c r="C1" t="s">
+        <v>718</v>
+      </c>
+      <c r="D1" t="s">
+        <v>737</v>
+      </c>
+      <c r="E1" t="s">
+        <v>738</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>739</v>
+      </c>
+      <c r="B2" t="s">
+        <v>741</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.234862</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>739</v>
+      </c>
+      <c r="B3" t="s">
+        <v>742</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-0.222222</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>739</v>
+      </c>
+      <c r="B4" t="s">
+        <v>743</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.227273</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>739</v>
+      </c>
+      <c r="B5" t="s">
+        <v>744</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.223485</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>740</v>
+      </c>
+      <c r="B6" t="s">
+        <v>745</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.262295</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>740</v>
+      </c>
+      <c r="B7" t="s">
+        <v>746</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.276364</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>740</v>
+      </c>
+      <c r="B8" t="s">
+        <v>747</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.267148</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>740</v>
+      </c>
+      <c r="B9" t="s">
+        <v>748</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.205607</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>740</v>
+      </c>
+      <c r="B10" t="s">
+        <v>749</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.182857</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>716</v>
+      </c>
+      <c r="B1" t="s">
+        <v>718</v>
+      </c>
+      <c r="C1" t="s">
+        <v>737</v>
+      </c>
+      <c r="D1" t="s">
+        <v>738</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>750</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.189032</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>751</v>
+      </c>
+      <c r="B3" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.178843</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>752</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.180547</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>753</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.179174</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>754</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.165032</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>755</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.163897</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>756</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.160643</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>757</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.15913</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>758</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.144495</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>759</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.932</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.226</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.140069</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>760</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.942</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.148233</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>761</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.125858</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>762</v>
+      </c>
+      <c r="B1" t="s">
+        <v>763</v>
+      </c>
+      <c r="C1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>765</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4.59</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>765</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C3" t="n">
+        <v>9.68</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>765</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C4" t="n">
+        <v>14.27</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>765</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C5" t="n">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>765</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>20.38</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>765</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="C7" t="n">
+        <v>20.38</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>765</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="C8" t="n">
+        <v>19.62</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>765</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="C9" t="n">
+        <v>20.89</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>765</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="C10" t="n">
+        <v>17.83</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>765</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="C11" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>765</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="C12" t="n">
+        <v>8.92</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>765</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="C13" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>765</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C14" t="n">
+        <v>9.68</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>765</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="C15" t="n">
+        <v>14.01</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>765</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="C16" t="n">
+        <v>19.62</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>765</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="C17" t="n">
+        <v>24.71</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>765</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="C18" t="n">
+        <v>29.81</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>765</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="C19" t="n">
+        <v>34.14</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>765</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="C20" t="n">
+        <v>37.2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>765</v>
+      </c>
+      <c r="B21" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="C21" t="n">
+        <v>34.39</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>765</v>
+      </c>
+      <c r="B22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C22" t="n">
+        <v>29.04</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>765</v>
+      </c>
+      <c r="B23" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="C23" t="n">
+        <v>25.48</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>765</v>
+      </c>
+      <c r="B24" t="n">
+        <v>0.56</v>
+      </c>
+      <c r="C24" t="n">
+        <v>21.66</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>765</v>
+      </c>
+      <c r="B25" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="C25" t="n">
+        <v>19.36</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>765</v>
+      </c>
+      <c r="B26" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="C26" t="n">
+        <v>16.56</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>765</v>
+      </c>
+      <c r="B27" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="C27" t="n">
+        <v>14.78</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>765</v>
+      </c>
+      <c r="B28" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C28" t="n">
+        <v>13.25</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>765</v>
+      </c>
+      <c r="B29" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="C29" t="n">
+        <v>11.97</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>765</v>
+      </c>
+      <c r="B30" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="C30" t="n">
+        <v>11.21</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>765</v>
+      </c>
+      <c r="B31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C31" t="n">
+        <v>9.94</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>765</v>
+      </c>
+      <c r="B32" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="C32" t="n">
+        <v>9.17</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>765</v>
+      </c>
+      <c r="B33" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="C33" t="n">
+        <v>9.17</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>765</v>
+      </c>
+      <c r="B34" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="C34" t="n">
+        <v>8.92</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>765</v>
+      </c>
+      <c r="B35" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C35" t="n">
+        <v>8.41</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>765</v>
+      </c>
+      <c r="B36" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="C36" t="n">
+        <v>7.39</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>765</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="C37" t="n">
+        <v>7.39</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>765</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="C38" t="n">
+        <v>7.39</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>765</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C39" t="n">
+        <v>7.39</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>765</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="C40" t="n">
+        <v>7.39</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>765</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="C41" t="n">
+        <v>7.39</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>765</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="C42" t="n">
+        <v>7.39</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>765</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C43" t="n">
+        <v>7.39</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>765</v>
+      </c>
+      <c r="B44" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="C44" t="n">
+        <v>7.39</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>765</v>
+      </c>
+      <c r="B45" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="C45" t="n">
+        <v>7.39</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>765</v>
+      </c>
+      <c r="B46" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="C46" t="n">
+        <v>7.39</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>765</v>
+      </c>
+      <c r="B47" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C47" t="n">
+        <v>7.39</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>765</v>
+      </c>
+      <c r="B48" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="C48" t="n">
+        <v>8.15</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>765</v>
+      </c>
+      <c r="B49" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="C49" t="n">
+        <v>8.41</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>765</v>
+      </c>
+      <c r="B50" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="C50" t="n">
+        <v>9.17</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>765</v>
+      </c>
+      <c r="B51" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C51" t="n">
+        <v>9.68</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>765</v>
+      </c>
+      <c r="B52" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="C52" t="n">
+        <v>9.94</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>765</v>
+      </c>
+      <c r="B53" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="C53" t="n">
+        <v>10.45</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>765</v>
+      </c>
+      <c r="B54" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C54" t="n">
+        <v>10.96</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>765</v>
+      </c>
+      <c r="B55" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C55" t="n">
+        <v>11.72</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>765</v>
+      </c>
+      <c r="B56" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="C56" t="n">
+        <v>11.97</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>765</v>
+      </c>
+      <c r="B57" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="C57" t="n">
+        <v>12.74</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>765</v>
+      </c>
+      <c r="B58" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="C58" t="n">
+        <v>13.25</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>765</v>
+      </c>
+      <c r="B59" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C59" t="n">
+        <v>14.01</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>765</v>
+      </c>
+      <c r="B60" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="C60" t="n">
+        <v>14.78</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>765</v>
+      </c>
+      <c r="B61" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="C61" t="n">
+        <v>15.03</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>765</v>
+      </c>
+      <c r="B62" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="C62" t="n">
+        <v>16.31</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>765</v>
+      </c>
+      <c r="B63" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="C63" t="n">
+        <v>16.56</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>766</v>
+      </c>
+      <c r="B64" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="C64" t="n">
+        <v>15.66</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>766</v>
+      </c>
+      <c r="B65" t="n">
+        <v>0.00711</v>
+      </c>
+      <c r="C65" t="n">
+        <v>16.02</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>766</v>
+      </c>
+      <c r="B66" t="n">
+        <v>0.01659</v>
+      </c>
+      <c r="C66" t="n">
+        <v>16.39</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>766</v>
+      </c>
+      <c r="B67" t="n">
+        <v>0.02133</v>
+      </c>
+      <c r="C67" t="n">
+        <v>16.57</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>766</v>
+      </c>
+      <c r="B68" t="n">
+        <v>0.02844</v>
+      </c>
+      <c r="C68" t="n">
+        <v>16.75</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>766</v>
+      </c>
+      <c r="B69" t="n">
+        <v>0.03555</v>
+      </c>
+      <c r="C69" t="n">
+        <v>17.06</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>766</v>
+      </c>
+      <c r="B70" t="n">
+        <v>0.04265</v>
+      </c>
+      <c r="C70" t="n">
+        <v>17.42</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>766</v>
+      </c>
+      <c r="B71" t="n">
+        <v>0.0545</v>
+      </c>
+      <c r="C71" t="n">
+        <v>17.78</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>766</v>
+      </c>
+      <c r="B72" t="n">
+        <v>0.06161</v>
+      </c>
+      <c r="C72" t="n">
+        <v>18.09</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>766</v>
+      </c>
+      <c r="B73" t="n">
+        <v>0.06872</v>
+      </c>
+      <c r="C73" t="n">
+        <v>18.27</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>766</v>
+      </c>
+      <c r="B74" t="n">
+        <v>0.07583</v>
+      </c>
+      <c r="C74" t="n">
+        <v>18.51</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>766</v>
+      </c>
+      <c r="B75" t="n">
+        <v>0.08531</v>
+      </c>
+      <c r="C75" t="n">
+        <v>18.82</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>766</v>
+      </c>
+      <c r="B76" t="n">
+        <v>0.09242</v>
+      </c>
+      <c r="C76" t="n">
+        <v>19.06</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>766</v>
+      </c>
+      <c r="B77" t="n">
+        <v>0.10427</v>
+      </c>
+      <c r="C77" t="n">
+        <v>19.42</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>766</v>
+      </c>
+      <c r="B78" t="n">
+        <v>0.11848</v>
+      </c>
+      <c r="C78" t="n">
+        <v>19.91</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>766</v>
+      </c>
+      <c r="B79" t="n">
+        <v>0.1327</v>
+      </c>
+      <c r="C79" t="n">
+        <v>20.27</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>766</v>
+      </c>
+      <c r="B80" t="n">
+        <v>0.14692</v>
+      </c>
+      <c r="C80" t="n">
+        <v>20.64</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>766</v>
+      </c>
+      <c r="B81" t="n">
+        <v>0.16114</v>
+      </c>
+      <c r="C81" t="n">
+        <v>21.0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>766</v>
+      </c>
+      <c r="B82" t="n">
+        <v>0.16825</v>
+      </c>
+      <c r="C82" t="n">
+        <v>21.31</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>766</v>
+      </c>
+      <c r="B83" t="n">
+        <v>0.18009</v>
+      </c>
+      <c r="C83" t="n">
+        <v>21.55</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>766</v>
+      </c>
+      <c r="B84" t="n">
+        <v>0.19668</v>
+      </c>
+      <c r="C84" t="n">
+        <v>21.55</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>766</v>
+      </c>
+      <c r="B85" t="n">
+        <v>0.2109</v>
+      </c>
+      <c r="C85" t="n">
+        <v>21.55</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>766</v>
+      </c>
+      <c r="B86" t="n">
+        <v>0.21801</v>
+      </c>
+      <c r="C86" t="n">
+        <v>21.85</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>766</v>
+      </c>
+      <c r="B87" t="n">
+        <v>0.22512</v>
+      </c>
+      <c r="C87" t="n">
+        <v>22.03</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>766</v>
+      </c>
+      <c r="B88" t="n">
+        <v>0.23697</v>
+      </c>
+      <c r="C88" t="n">
+        <v>22.22</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>766</v>
+      </c>
+      <c r="B89" t="n">
+        <v>0.25118</v>
+      </c>
+      <c r="C89" t="n">
+        <v>22.03</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>766</v>
+      </c>
+      <c r="B90" t="n">
+        <v>0.25592</v>
+      </c>
+      <c r="C90" t="n">
+        <v>21.73</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>766</v>
+      </c>
+      <c r="B91" t="n">
+        <v>0.25829</v>
+      </c>
+      <c r="C91" t="n">
+        <v>21.49</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>766</v>
+      </c>
+      <c r="B92" t="n">
+        <v>0.26303</v>
+      </c>
+      <c r="C92" t="n">
+        <v>21.18</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>766</v>
+      </c>
+      <c r="B93" t="n">
+        <v>0.26303</v>
+      </c>
+      <c r="C93" t="n">
+        <v>20.82</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>766</v>
+      </c>
+      <c r="B94" t="n">
+        <v>0.27014</v>
+      </c>
+      <c r="C94" t="n">
+        <v>20.27</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>766</v>
+      </c>
+      <c r="B95" t="n">
+        <v>0.27014</v>
+      </c>
+      <c r="C95" t="n">
+        <v>19.97</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>766</v>
+      </c>
+      <c r="B96" t="n">
+        <v>0.27251</v>
+      </c>
+      <c r="C96" t="n">
+        <v>19.42</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>766</v>
+      </c>
+      <c r="B97" t="n">
+        <v>0.27251</v>
+      </c>
+      <c r="C97" t="n">
+        <v>19.18</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>766</v>
+      </c>
+      <c r="B98" t="n">
+        <v>0.27251</v>
+      </c>
+      <c r="C98" t="n">
+        <v>18.88</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>766</v>
+      </c>
+      <c r="B99" t="n">
+        <v>0.27725</v>
+      </c>
+      <c r="C99" t="n">
+        <v>18.33</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>766</v>
+      </c>
+      <c r="B100" t="n">
+        <v>0.27962</v>
+      </c>
+      <c r="C100" t="n">
+        <v>17.97</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>766</v>
+      </c>
+      <c r="B101" t="n">
+        <v>0.27725</v>
+      </c>
+      <c r="C101" t="n">
+        <v>17.48</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>766</v>
+      </c>
+      <c r="B102" t="n">
+        <v>0.27962</v>
+      </c>
+      <c r="C102" t="n">
+        <v>16.69</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>766</v>
+      </c>
+      <c r="B103" t="n">
+        <v>0.27962</v>
+      </c>
+      <c r="C103" t="n">
+        <v>16.15</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>766</v>
+      </c>
+      <c r="B104" t="n">
+        <v>0.27962</v>
+      </c>
+      <c r="C104" t="n">
+        <v>15.11</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>766</v>
+      </c>
+      <c r="B105" t="n">
+        <v>0.28436</v>
+      </c>
+      <c r="C105" t="n">
+        <v>16.33</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>766</v>
+      </c>
+      <c r="B106" t="n">
+        <v>0.29147</v>
+      </c>
+      <c r="C106" t="n">
+        <v>16.75</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>766</v>
+      </c>
+      <c r="B107" t="n">
+        <v>0.29147</v>
+      </c>
+      <c r="C107" t="n">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>766</v>
+      </c>
+      <c r="B108" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="C108" t="n">
+        <v>17.78</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>766</v>
+      </c>
+      <c r="B109" t="n">
+        <v>0.30806</v>
+      </c>
+      <c r="C109" t="n">
+        <v>16.87</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>766</v>
+      </c>
+      <c r="B110" t="n">
+        <v>0.3128</v>
+      </c>
+      <c r="C110" t="n">
+        <v>17.78</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>766</v>
+      </c>
+      <c r="B111" t="n">
+        <v>0.31517</v>
+      </c>
+      <c r="C111" t="n">
+        <v>18.15</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>766</v>
+      </c>
+      <c r="B112" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="C112" t="n">
+        <v>18.33</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>766</v>
+      </c>
+      <c r="B113" t="n">
+        <v>0.32701</v>
+      </c>
+      <c r="C113" t="n">
+        <v>18.69</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>766</v>
+      </c>
+      <c r="B114" t="n">
+        <v>0.33649</v>
+      </c>
+      <c r="C114" t="n">
+        <v>19.18</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>766</v>
+      </c>
+      <c r="B115" t="n">
+        <v>0.34834</v>
+      </c>
+      <c r="C115" t="n">
+        <v>19.24</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>766</v>
+      </c>
+      <c r="B116" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="C116" t="n">
+        <v>19.42</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>766</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="C117" t="n">
+        <v>19.79</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>766</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="C118" t="n">
+        <v>20.15</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>766</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.37441</v>
+      </c>
+      <c r="C119" t="n">
+        <v>19.54</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>766</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.38152</v>
+      </c>
+      <c r="C120" t="n">
+        <v>19.06</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>766</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.38863</v>
+      </c>
+      <c r="C121" t="n">
+        <v>18.82</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>766</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.3981</v>
+      </c>
+      <c r="C122" t="n">
+        <v>17.91</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>766</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.40284</v>
+      </c>
+      <c r="C123" t="n">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>766</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.40521</v>
+      </c>
+      <c r="C124" t="n">
+        <v>16.87</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>766</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.40521</v>
+      </c>
+      <c r="C125" t="n">
+        <v>16.51</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>766</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.40521</v>
+      </c>
+      <c r="C126" t="n">
+        <v>15.66</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>766</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.40521</v>
+      </c>
+      <c r="C127" t="n">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>766</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.41232</v>
+      </c>
+      <c r="C128" t="n">
+        <v>14.57</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>766</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.41232</v>
+      </c>
+      <c r="C129" t="n">
+        <v>12.32</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>766</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.41706</v>
+      </c>
+      <c r="C130" t="n">
+        <v>11.41</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>766</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.42417</v>
+      </c>
+      <c r="C131" t="n">
+        <v>10.86</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>766</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.42654</v>
+      </c>
+      <c r="C132" t="n">
+        <v>10.68</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>766</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.43365</v>
+      </c>
+      <c r="C133" t="n">
+        <v>12.63</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>766</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.43365</v>
+      </c>
+      <c r="C134" t="n">
+        <v>13.66</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>766</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.43839</v>
+      </c>
+      <c r="C135" t="n">
+        <v>14.45</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>766</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.44076</v>
+      </c>
+      <c r="C136" t="n">
+        <v>17.42</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>766</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.44076</v>
+      </c>
+      <c r="C137" t="n">
+        <v>19.36</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>766</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.4455</v>
+      </c>
+      <c r="C138" t="n">
+        <v>19.79</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>766</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.44787</v>
+      </c>
+      <c r="C139" t="n">
+        <v>20.09</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>766</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.45261</v>
+      </c>
+      <c r="C140" t="n">
+        <v>21.67</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>766</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.45735</v>
+      </c>
+      <c r="C141" t="n">
+        <v>21.91</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>766</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.45972</v>
+      </c>
+      <c r="C142" t="n">
+        <v>27.01</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>766</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.46445</v>
+      </c>
+      <c r="C143" t="n">
+        <v>29.01</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>766</v>
+      </c>
+      <c r="B144" t="n">
+        <v>0.47156</v>
+      </c>
+      <c r="C144" t="n">
+        <v>29.56</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>766</v>
+      </c>
+      <c r="B145" t="n">
+        <v>0.47867</v>
+      </c>
+      <c r="C145" t="n">
+        <v>30.71</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>766</v>
+      </c>
+      <c r="B146" t="n">
+        <v>0.48578</v>
+      </c>
+      <c r="C146" t="n">
+        <v>32.41</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>766</v>
+      </c>
+      <c r="B147" t="n">
+        <v>0.49526</v>
+      </c>
+      <c r="C147" t="n">
+        <v>30.77</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>766</v>
+      </c>
+      <c r="B148" t="n">
+        <v>0.49289</v>
+      </c>
+      <c r="C148" t="n">
+        <v>28.95</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>766</v>
+      </c>
+      <c r="B149" t="n">
+        <v>0.49526</v>
+      </c>
+      <c r="C149" t="n">
+        <v>28.1</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>766</v>
+      </c>
+      <c r="B150" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C150" t="n">
+        <v>26.89</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>766</v>
+      </c>
+      <c r="B151" t="n">
+        <v>0.50711</v>
+      </c>
+      <c r="C151" t="n">
+        <v>24.89</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>766</v>
+      </c>
+      <c r="B152" t="n">
+        <v>0.50711</v>
+      </c>
+      <c r="C152" t="n">
+        <v>24.34</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>766</v>
+      </c>
+      <c r="B153" t="n">
+        <v>0.51422</v>
+      </c>
+      <c r="C153" t="n">
+        <v>25.55</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>766</v>
+      </c>
+      <c r="B154" t="n">
+        <v>0.53081</v>
+      </c>
+      <c r="C154" t="n">
+        <v>26.53</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>766</v>
+      </c>
+      <c r="B155" t="n">
+        <v>0.53081</v>
+      </c>
+      <c r="C155" t="n">
+        <v>28.29</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>766</v>
+      </c>
+      <c r="B156" t="n">
+        <v>0.53555</v>
+      </c>
+      <c r="C156" t="n">
+        <v>28.83</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>766</v>
+      </c>
+      <c r="B157" t="n">
+        <v>0.54265</v>
+      </c>
+      <c r="C157" t="n">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>766</v>
+      </c>
+      <c r="B158" t="n">
+        <v>0.53791</v>
+      </c>
+      <c r="C158" t="n">
+        <v>30.96</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>766</v>
+      </c>
+      <c r="B159" t="n">
+        <v>0.5545</v>
+      </c>
+      <c r="C159" t="n">
+        <v>30.41</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>766</v>
+      </c>
+      <c r="B160" t="n">
+        <v>0.55687</v>
+      </c>
+      <c r="C160" t="n">
+        <v>28.95</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>766</v>
+      </c>
+      <c r="B161" t="n">
+        <v>0.56161</v>
+      </c>
+      <c r="C161" t="n">
+        <v>27.56</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>766</v>
+      </c>
+      <c r="B162" t="n">
+        <v>0.56398</v>
+      </c>
+      <c r="C162" t="n">
+        <v>26.46</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>766</v>
+      </c>
+      <c r="B163" t="n">
+        <v>0.56398</v>
+      </c>
+      <c r="C163" t="n">
+        <v>25.61</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>766</v>
+      </c>
+      <c r="B164" t="n">
+        <v>0.56872</v>
+      </c>
+      <c r="C164" t="n">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>766</v>
+      </c>
+      <c r="B165" t="n">
+        <v>0.5782</v>
+      </c>
+      <c r="C165" t="n">
+        <v>23.61</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>766</v>
+      </c>
+      <c r="B166" t="n">
+        <v>0.5782</v>
+      </c>
+      <c r="C166" t="n">
+        <v>22.64</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>766</v>
+      </c>
+      <c r="B167" t="n">
+        <v>0.58294</v>
+      </c>
+      <c r="C167" t="n">
+        <v>21.55</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>766</v>
+      </c>
+      <c r="B168" t="n">
+        <v>0.58531</v>
+      </c>
+      <c r="C168" t="n">
+        <v>20.76</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>766</v>
+      </c>
+      <c r="B169" t="n">
+        <v>0.59005</v>
+      </c>
+      <c r="C169" t="n">
+        <v>19.24</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>766</v>
+      </c>
+      <c r="B170" t="n">
+        <v>0.59005</v>
+      </c>
+      <c r="C170" t="n">
+        <v>18.15</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>766</v>
+      </c>
+      <c r="B171" t="n">
+        <v>0.59005</v>
+      </c>
+      <c r="C171" t="n">
+        <v>16.02</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>766</v>
+      </c>
+      <c r="B172" t="n">
+        <v>0.60664</v>
+      </c>
+      <c r="C172" t="n">
+        <v>19.06</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>766</v>
+      </c>
+      <c r="B173" t="n">
+        <v>0.62085</v>
+      </c>
+      <c r="C173" t="n">
+        <v>16.57</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>766</v>
+      </c>
+      <c r="B174" t="n">
+        <v>0.62559</v>
+      </c>
+      <c r="C174" t="n">
+        <v>19.79</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>766</v>
+      </c>
+      <c r="B175" t="n">
+        <v>0.62796</v>
+      </c>
+      <c r="C175" t="n">
+        <v>21.91</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>766</v>
+      </c>
+      <c r="B176" t="n">
+        <v>0.62796</v>
+      </c>
+      <c r="C176" t="n">
+        <v>22.94</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>766</v>
+      </c>
+      <c r="B177" t="n">
+        <v>0.6327</v>
+      </c>
+      <c r="C177" t="n">
+        <v>23.67</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>766</v>
+      </c>
+      <c r="B178" t="n">
+        <v>0.6327</v>
+      </c>
+      <c r="C178" t="n">
+        <v>24.76</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>766</v>
+      </c>
+      <c r="B179" t="n">
+        <v>0.63507</v>
+      </c>
+      <c r="C179" t="n">
+        <v>25.55</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>766</v>
+      </c>
+      <c r="B180" t="n">
+        <v>0.64218</v>
+      </c>
+      <c r="C180" t="n">
+        <v>26.28</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>766</v>
+      </c>
+      <c r="B181" t="n">
+        <v>0.64929</v>
+      </c>
+      <c r="C181" t="n">
+        <v>27.19</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>766</v>
+      </c>
+      <c r="B182" t="n">
+        <v>0.66114</v>
+      </c>
+      <c r="C182" t="n">
+        <v>28.59</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>766</v>
+      </c>
+      <c r="B183" t="n">
+        <v>0.66825</v>
+      </c>
+      <c r="C183" t="n">
+        <v>25.43</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>766</v>
+      </c>
+      <c r="B184" t="n">
+        <v>0.66825</v>
+      </c>
+      <c r="C184" t="n">
+        <v>24.76</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>766</v>
+      </c>
+      <c r="B185" t="n">
+        <v>0.66825</v>
+      </c>
+      <c r="C185" t="n">
+        <v>23.85</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>766</v>
+      </c>
+      <c r="B186" t="n">
+        <v>0.68009</v>
+      </c>
+      <c r="C186" t="n">
+        <v>22.94</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>766</v>
+      </c>
+      <c r="B187" t="n">
+        <v>0.68957</v>
+      </c>
+      <c r="C187" t="n">
+        <v>22.03</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>766</v>
+      </c>
+      <c r="B188" t="n">
+        <v>0.70853</v>
+      </c>
+      <c r="C188" t="n">
+        <v>21.37</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>766</v>
+      </c>
+      <c r="B189" t="n">
+        <v>0.70853</v>
+      </c>
+      <c r="C189" t="n">
+        <v>18.88</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>766</v>
+      </c>
+      <c r="B190" t="n">
+        <v>0.7109</v>
+      </c>
+      <c r="C190" t="n">
+        <v>23.61</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>766</v>
+      </c>
+      <c r="B191" t="n">
+        <v>0.71564</v>
+      </c>
+      <c r="C191" t="n">
+        <v>26.71</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>766</v>
+      </c>
+      <c r="B192" t="n">
+        <v>0.73697</v>
+      </c>
+      <c r="C192" t="n">
+        <v>21.85</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>766</v>
+      </c>
+      <c r="B193" t="n">
+        <v>0.75118</v>
+      </c>
+      <c r="C193" t="n">
+        <v>22.94</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>766</v>
+      </c>
+      <c r="B194" t="n">
+        <v>0.75829</v>
+      </c>
+      <c r="C194" t="n">
+        <v>23.67</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>766</v>
+      </c>
+      <c r="B195" t="n">
+        <v>0.75592</v>
+      </c>
+      <c r="C195" t="n">
+        <v>25.37</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>766</v>
+      </c>
+      <c r="B196" t="n">
+        <v>0.75829</v>
+      </c>
+      <c r="C196" t="n">
+        <v>25.43</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>766</v>
+      </c>
+      <c r="B197" t="n">
+        <v>0.77014</v>
+      </c>
+      <c r="C197" t="n">
+        <v>25.98</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>766</v>
+      </c>
+      <c r="B198" t="n">
+        <v>0.78673</v>
+      </c>
+      <c r="C198" t="n">
+        <v>25.74</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>766</v>
+      </c>
+      <c r="B199" t="n">
+        <v>0.80806</v>
+      </c>
+      <c r="C199" t="n">
+        <v>25.74</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>766</v>
+      </c>
+      <c r="B200" t="n">
+        <v>0.82227</v>
+      </c>
+      <c r="C200" t="n">
+        <v>24.58</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>766</v>
+      </c>
+      <c r="B201" t="n">
+        <v>0.85545</v>
+      </c>
+      <c r="C201" t="n">
+        <v>23.13</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="s">
+        <v>766</v>
+      </c>
+      <c r="B202" t="n">
+        <v>0.86019</v>
+      </c>
+      <c r="C202" t="n">
+        <v>22.22</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="s">
+        <v>766</v>
+      </c>
+      <c r="B203" t="n">
+        <v>0.8673</v>
+      </c>
+      <c r="C203" t="n">
+        <v>21.49</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="s">
+        <v>766</v>
+      </c>
+      <c r="B204" t="n">
+        <v>0.88152</v>
+      </c>
+      <c r="C204" t="n">
+        <v>20.58</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="s">
+        <v>766</v>
+      </c>
+      <c r="B205" t="n">
+        <v>0.891</v>
+      </c>
+      <c r="C205" t="n">
+        <v>20.09</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="s">
+        <v>766</v>
+      </c>
+      <c r="B206" t="n">
+        <v>0.891</v>
+      </c>
+      <c r="C206" t="n">
+        <v>19.73</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="s">
+        <v>766</v>
+      </c>
+      <c r="B207" t="n">
+        <v>0.90995</v>
+      </c>
+      <c r="C207" t="n">
+        <v>19.42</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="s">
+        <v>766</v>
+      </c>
+      <c r="B208" t="n">
+        <v>0.92417</v>
+      </c>
+      <c r="C208" t="n">
+        <v>19.0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="s">
+        <v>766</v>
+      </c>
+      <c r="B209" t="n">
+        <v>0.93365</v>
+      </c>
+      <c r="C209" t="n">
+        <v>18.51</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="s">
+        <v>766</v>
+      </c>
+      <c r="B210" t="n">
+        <v>0.95735</v>
+      </c>
+      <c r="C210" t="n">
+        <v>17.78</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="s">
+        <v>766</v>
+      </c>
+      <c r="B211" t="n">
+        <v>0.96445</v>
+      </c>
+      <c r="C211" t="n">
+        <v>17.48</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="s">
+        <v>766</v>
+      </c>
+      <c r="B212" t="n">
+        <v>0.98104</v>
+      </c>
+      <c r="C212" t="n">
+        <v>16.93</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="s">
+        <v>766</v>
+      </c>
+      <c r="B213" t="n">
+        <v>0.98578</v>
+      </c>
+      <c r="C213" t="n">
+        <v>16.39</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="s">
+        <v>766</v>
+      </c>
+      <c r="B214" t="n">
+        <v>0.99526</v>
+      </c>
+      <c r="C214" t="n">
+        <v>15.66</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="s">
+        <v>766</v>
+      </c>
+      <c r="B215" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="C215" t="n">
+        <v>15.24</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="s">
+        <v>766</v>
+      </c>
+      <c r="B216" t="n">
+        <v>1.00711</v>
+      </c>
+      <c r="C216" t="n">
+        <v>14.26</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="s">
+        <v>766</v>
+      </c>
+      <c r="B217" t="n">
+        <v>1.00711</v>
+      </c>
+      <c r="C217" t="n">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="s">
+        <v>766</v>
+      </c>
+      <c r="B218" t="n">
+        <v>1.06872</v>
+      </c>
+      <c r="C218" t="n">
+        <v>13.84</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="s">
+        <v>766</v>
+      </c>
+      <c r="B219" t="n">
+        <v>1.08531</v>
+      </c>
+      <c r="C219" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="s">
+        <v>766</v>
+      </c>
+      <c r="B220" t="n">
+        <v>1.11137</v>
+      </c>
+      <c r="C220" t="n">
+        <v>12.32</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="s">
+        <v>766</v>
+      </c>
+      <c r="B221" t="n">
+        <v>1.12559</v>
+      </c>
+      <c r="C221" t="n">
+        <v>11.71</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="s">
+        <v>766</v>
+      </c>
+      <c r="B222" t="n">
+        <v>1.14692</v>
+      </c>
+      <c r="C222" t="n">
+        <v>11.41</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="s">
+        <v>766</v>
+      </c>
+      <c r="B223" t="n">
+        <v>1.16588</v>
+      </c>
+      <c r="C223" t="n">
+        <v>11.17</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="s">
+        <v>766</v>
+      </c>
+      <c r="B224" t="n">
+        <v>1.1872</v>
+      </c>
+      <c r="C224" t="n">
+        <v>10.68</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="s">
+        <v>766</v>
+      </c>
+      <c r="B225" t="n">
+        <v>1.1872</v>
+      </c>
+      <c r="C225" t="n">
+        <v>10.08</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="s">
+        <v>766</v>
+      </c>
+      <c r="B226" t="n">
+        <v>1.19668</v>
+      </c>
+      <c r="C226" t="n">
+        <v>11.35</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="s">
+        <v>766</v>
+      </c>
+      <c r="B227" t="n">
+        <v>1.20379</v>
+      </c>
+      <c r="C227" t="n">
+        <v>12.14</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="s">
+        <v>766</v>
+      </c>
+      <c r="B228" t="n">
+        <v>1.2109</v>
+      </c>
+      <c r="C228" t="n">
+        <v>12.93</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="s">
+        <v>766</v>
+      </c>
+      <c r="B229" t="n">
+        <v>1.21564</v>
+      </c>
+      <c r="C229" t="n">
+        <v>14.63</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="s">
+        <v>766</v>
+      </c>
+      <c r="B230" t="n">
+        <v>1.21564</v>
+      </c>
+      <c r="C230" t="n">
+        <v>16.33</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="s">
+        <v>766</v>
+      </c>
+      <c r="B231" t="n">
+        <v>1.21801</v>
+      </c>
+      <c r="C231" t="n">
+        <v>21.12</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="s">
+        <v>766</v>
+      </c>
+      <c r="B232" t="n">
+        <v>1.22275</v>
+      </c>
+      <c r="C232" t="n">
+        <v>22.64</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="s">
+        <v>766</v>
+      </c>
+      <c r="B233" t="n">
+        <v>1.22986</v>
+      </c>
+      <c r="C233" t="n">
+        <v>23.13</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="s">
+        <v>766</v>
+      </c>
+      <c r="B234" t="n">
+        <v>1.23223</v>
+      </c>
+      <c r="C234" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="s">
+        <v>766</v>
+      </c>
+      <c r="B235" t="n">
+        <v>1.23934</v>
+      </c>
+      <c r="C235" t="n">
+        <v>27.62</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="s">
+        <v>766</v>
+      </c>
+      <c r="B236" t="n">
+        <v>1.24645</v>
+      </c>
+      <c r="C236" t="n">
+        <v>24.95</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="s">
+        <v>766</v>
+      </c>
+      <c r="B237" t="n">
+        <v>1.25118</v>
+      </c>
+      <c r="C237" t="n">
+        <v>22.76</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="s">
+        <v>766</v>
+      </c>
+      <c r="B238" t="n">
+        <v>1.25829</v>
+      </c>
+      <c r="C238" t="n">
+        <v>21.85</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="s">
+        <v>766</v>
+      </c>
+      <c r="B239" t="n">
+        <v>1.25829</v>
+      </c>
+      <c r="C239" t="n">
+        <v>20.15</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="s">
+        <v>766</v>
+      </c>
+      <c r="B240" t="n">
+        <v>1.27014</v>
+      </c>
+      <c r="C240" t="n">
+        <v>24.89</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="s">
+        <v>766</v>
+      </c>
+      <c r="B241" t="n">
+        <v>1.28436</v>
+      </c>
+      <c r="C241" t="n">
+        <v>25.37</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="s">
+        <v>766</v>
+      </c>
+      <c r="B242" t="n">
+        <v>1.28673</v>
+      </c>
+      <c r="C242" t="n">
+        <v>25.74</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="s">
+        <v>766</v>
+      </c>
+      <c r="B243" t="n">
+        <v>1.29384</v>
+      </c>
+      <c r="C243" t="n">
+        <v>26.65</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="s">
+        <v>766</v>
+      </c>
+      <c r="B244" t="n">
+        <v>1.29858</v>
+      </c>
+      <c r="C244" t="n">
+        <v>27.25</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="s">
+        <v>766</v>
+      </c>
+      <c r="B245" t="n">
+        <v>1.29858</v>
+      </c>
+      <c r="C245" t="n">
+        <v>28.65</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="s">
+        <v>766</v>
+      </c>
+      <c r="B246" t="n">
+        <v>1.29858</v>
+      </c>
+      <c r="C246" t="n">
+        <v>29.86</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="s">
+        <v>766</v>
+      </c>
+      <c r="B247" t="n">
+        <v>1.30569</v>
+      </c>
+      <c r="C247" t="n">
+        <v>30.71</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="s">
+        <v>766</v>
+      </c>
+      <c r="B248" t="n">
+        <v>1.3128</v>
+      </c>
+      <c r="C248" t="n">
+        <v>32.17</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="s">
+        <v>766</v>
+      </c>
+      <c r="B249" t="n">
+        <v>1.32227</v>
+      </c>
+      <c r="C249" t="n">
+        <v>30.23</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="s">
+        <v>766</v>
+      </c>
+      <c r="B250" t="n">
+        <v>1.32227</v>
+      </c>
+      <c r="C250" t="n">
+        <v>28.59</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="s">
+        <v>766</v>
+      </c>
+      <c r="B251" t="n">
+        <v>1.32938</v>
+      </c>
+      <c r="C251" t="n">
+        <v>27.74</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="s">
+        <v>766</v>
+      </c>
+      <c r="B252" t="n">
+        <v>1.33649</v>
+      </c>
+      <c r="C252" t="n">
+        <v>27.01</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="s">
+        <v>766</v>
+      </c>
+      <c r="B253" t="n">
+        <v>1.35308</v>
+      </c>
+      <c r="C253" t="n">
+        <v>26.53</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="s">
+        <v>766</v>
+      </c>
+      <c r="B254" t="n">
+        <v>1.36256</v>
+      </c>
+      <c r="C254" t="n">
+        <v>25.55</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="s">
+        <v>766</v>
+      </c>
+      <c r="B255" t="n">
+        <v>1.36967</v>
+      </c>
+      <c r="C255" t="n">
+        <v>24.34</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="s">
+        <v>766</v>
+      </c>
+      <c r="B256" t="n">
+        <v>1.38389</v>
+      </c>
+      <c r="C256" t="n">
+        <v>23.07</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="s">
+        <v>766</v>
+      </c>
+      <c r="B257" t="n">
+        <v>1.391</v>
+      </c>
+      <c r="C257" t="n">
+        <v>21.55</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="s">
+        <v>766</v>
+      </c>
+      <c r="B258" t="n">
+        <v>1.3981</v>
+      </c>
+      <c r="C258" t="n">
+        <v>18.63</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="s">
+        <v>766</v>
+      </c>
+      <c r="B259" t="n">
+        <v>1.3981</v>
+      </c>
+      <c r="C259" t="n">
+        <v>17.06</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="s">
+        <v>766</v>
+      </c>
+      <c r="B260" t="n">
+        <v>1.40284</v>
+      </c>
+      <c r="C260" t="n">
+        <v>16.02</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="s">
+        <v>766</v>
+      </c>
+      <c r="B261" t="n">
+        <v>1.40284</v>
+      </c>
+      <c r="C261" t="n">
+        <v>14.81</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="s">
+        <v>766</v>
+      </c>
+      <c r="B262" t="n">
+        <v>1.41232</v>
+      </c>
+      <c r="C262" t="n">
+        <v>13.84</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="s">
+        <v>766</v>
+      </c>
+      <c r="B263" t="n">
+        <v>1.42654</v>
+      </c>
+      <c r="C263" t="n">
+        <v>16.02</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="s">
+        <v>766</v>
+      </c>
+      <c r="B264" t="n">
+        <v>1.43365</v>
+      </c>
+      <c r="C264" t="n">
+        <v>16.93</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="s">
+        <v>766</v>
+      </c>
+      <c r="B265" t="n">
+        <v>1.4455</v>
+      </c>
+      <c r="C265" t="n">
+        <v>15.84</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="s">
+        <v>766</v>
+      </c>
+      <c r="B266" t="n">
+        <v>1.4455</v>
+      </c>
+      <c r="C266" t="n">
+        <v>14.81</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="s">
+        <v>766</v>
+      </c>
+      <c r="B267" t="n">
+        <v>1.4455</v>
+      </c>
+      <c r="C267" t="n">
+        <v>14.39</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="s">
+        <v>766</v>
+      </c>
+      <c r="B268" t="n">
+        <v>1.44787</v>
+      </c>
+      <c r="C268" t="n">
+        <v>13.47</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="s">
+        <v>766</v>
+      </c>
+      <c r="B269" t="n">
+        <v>1.45735</v>
+      </c>
+      <c r="C269" t="n">
+        <v>12.32</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="s">
+        <v>766</v>
+      </c>
+      <c r="B270" t="n">
+        <v>1.45972</v>
+      </c>
+      <c r="C270" t="n">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="s">
+        <v>766</v>
+      </c>
+      <c r="B271" t="n">
+        <v>1.47867</v>
+      </c>
+      <c r="C271" t="n">
+        <v>12.93</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="s">
+        <v>766</v>
+      </c>
+      <c r="B272" t="n">
+        <v>1.47867</v>
+      </c>
+      <c r="C272" t="n">
+        <v>13.72</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="s">
+        <v>766</v>
+      </c>
+      <c r="B273" t="n">
+        <v>1.48104</v>
+      </c>
+      <c r="C273" t="n">
+        <v>14.39</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="s">
+        <v>766</v>
+      </c>
+      <c r="B274" t="n">
+        <v>1.48578</v>
+      </c>
+      <c r="C274" t="n">
+        <v>15.48</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="s">
+        <v>766</v>
+      </c>
+      <c r="B275" t="n">
+        <v>1.49289</v>
+      </c>
+      <c r="C275" t="n">
+        <v>16.39</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="s">
+        <v>766</v>
+      </c>
+      <c r="B276" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C276" t="n">
+        <v>17.97</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="s">
+        <v>766</v>
+      </c>
+      <c r="B277" t="n">
+        <v>1.50711</v>
+      </c>
+      <c r="C277" t="n">
+        <v>16.21</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="s">
+        <v>766</v>
+      </c>
+      <c r="B278" t="n">
+        <v>1.50948</v>
+      </c>
+      <c r="C278" t="n">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="s">
+        <v>766</v>
+      </c>
+      <c r="B279" t="n">
+        <v>1.51659</v>
+      </c>
+      <c r="C279" t="n">
+        <v>14.63</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="s">
+        <v>766</v>
+      </c>
+      <c r="B280" t="n">
+        <v>1.52844</v>
+      </c>
+      <c r="C280" t="n">
+        <v>13.29</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="s">
+        <v>766</v>
+      </c>
+      <c r="B281" t="n">
+        <v>1.52844</v>
+      </c>
+      <c r="C281" t="n">
+        <v>12.44</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="s">
+        <v>766</v>
+      </c>
+      <c r="B282" t="n">
+        <v>1.54976</v>
+      </c>
+      <c r="C282" t="n">
+        <v>12.26</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="s">
+        <v>766</v>
+      </c>
+      <c r="B283" t="n">
+        <v>1.56161</v>
+      </c>
+      <c r="C283" t="n">
+        <v>11.53</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="s">
+        <v>766</v>
+      </c>
+      <c r="B284" t="n">
+        <v>1.5782</v>
+      </c>
+      <c r="C284" t="n">
+        <v>11.17</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="s">
+        <v>766</v>
+      </c>
+      <c r="B285" t="n">
+        <v>1.58531</v>
+      </c>
+      <c r="C285" t="n">
+        <v>11.59</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="s">
+        <v>766</v>
+      </c>
+      <c r="B286" t="n">
+        <v>1.59242</v>
+      </c>
+      <c r="C286" t="n">
+        <v>12.14</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="s">
+        <v>766</v>
+      </c>
+      <c r="B287" t="n">
+        <v>1.61137</v>
+      </c>
+      <c r="C287" t="n">
+        <v>12.32</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="s">
+        <v>766</v>
+      </c>
+      <c r="B288" t="n">
+        <v>1.62085</v>
+      </c>
+      <c r="C288" t="n">
+        <v>11.96</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="s">
+        <v>766</v>
+      </c>
+      <c r="B289" t="n">
+        <v>1.63507</v>
+      </c>
+      <c r="C289" t="n">
+        <v>11.71</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="s">
+        <v>766</v>
+      </c>
+      <c r="B290" t="n">
+        <v>1.64218</v>
+      </c>
+      <c r="C290" t="n">
+        <v>12.14</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="s">
+        <v>766</v>
+      </c>
+      <c r="B291" t="n">
+        <v>1.64692</v>
+      </c>
+      <c r="C291" t="n">
+        <v>12.75</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="s">
+        <v>766</v>
+      </c>
+      <c r="B292" t="n">
+        <v>1.64692</v>
+      </c>
+      <c r="C292" t="n">
+        <v>13.66</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="s">
+        <v>766</v>
+      </c>
+      <c r="B293" t="n">
+        <v>1.65403</v>
+      </c>
+      <c r="C293" t="n">
+        <v>15.24</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="s">
+        <v>766</v>
+      </c>
+      <c r="B294" t="n">
+        <v>1.65877</v>
+      </c>
+      <c r="C294" t="n">
+        <v>16.39</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="s">
+        <v>766</v>
+      </c>
+      <c r="B295" t="n">
+        <v>1.66114</v>
+      </c>
+      <c r="C295" t="n">
+        <v>16.87</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="s">
+        <v>766</v>
+      </c>
+      <c r="B296" t="n">
+        <v>1.66114</v>
+      </c>
+      <c r="C296" t="n">
+        <v>17.91</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="s">
+        <v>766</v>
+      </c>
+      <c r="B297" t="n">
+        <v>1.66825</v>
+      </c>
+      <c r="C297" t="n">
+        <v>18.09</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="s">
+        <v>766</v>
+      </c>
+      <c r="B298" t="n">
+        <v>1.6872</v>
+      </c>
+      <c r="C298" t="n">
+        <v>17.91</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="s">
+        <v>766</v>
+      </c>
+      <c r="B299" t="n">
+        <v>1.68957</v>
+      </c>
+      <c r="C299" t="n">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="s">
+        <v>766</v>
+      </c>
+      <c r="B300" t="n">
+        <v>1.70142</v>
+      </c>
+      <c r="C300" t="n">
+        <v>18.45</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="s">
+        <v>766</v>
+      </c>
+      <c r="B301" t="n">
+        <v>1.70142</v>
+      </c>
+      <c r="C301" t="n">
+        <v>19.06</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="s">
+        <v>766</v>
+      </c>
+      <c r="B302" t="n">
+        <v>1.70853</v>
+      </c>
+      <c r="C302" t="n">
+        <v>19.73</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="s">
+        <v>766</v>
+      </c>
+      <c r="B303" t="n">
+        <v>1.7109</v>
+      </c>
+      <c r="C303" t="n">
+        <v>20.82</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="s">
+        <v>766</v>
+      </c>
+      <c r="B304" t="n">
+        <v>1.7109</v>
+      </c>
+      <c r="C304" t="n">
+        <v>22.22</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="s">
+        <v>766</v>
+      </c>
+      <c r="B305" t="n">
+        <v>1.71564</v>
+      </c>
+      <c r="C305" t="n">
+        <v>23.13</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="s">
+        <v>766</v>
+      </c>
+      <c r="B306" t="n">
+        <v>1.71564</v>
+      </c>
+      <c r="C306" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="s">
+        <v>766</v>
+      </c>
+      <c r="B307" t="n">
+        <v>1.71801</v>
+      </c>
+      <c r="C307" t="n">
+        <v>24.89</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="s">
+        <v>766</v>
+      </c>
+      <c r="B308" t="n">
+        <v>1.72512</v>
+      </c>
+      <c r="C308" t="n">
+        <v>25.37</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="s">
+        <v>766</v>
+      </c>
+      <c r="B309" t="n">
+        <v>1.72986</v>
+      </c>
+      <c r="C309" t="n">
+        <v>25.98</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="s">
+        <v>766</v>
+      </c>
+      <c r="B310" t="n">
+        <v>1.73934</v>
+      </c>
+      <c r="C310" t="n">
+        <v>25.61</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="s">
+        <v>766</v>
+      </c>
+      <c r="B311" t="n">
+        <v>1.76303</v>
+      </c>
+      <c r="C311" t="n">
+        <v>25.07</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="s">
+        <v>766</v>
+      </c>
+      <c r="B312" t="n">
+        <v>1.78436</v>
+      </c>
+      <c r="C312" t="n">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="s">
+        <v>766</v>
+      </c>
+      <c r="B313" t="n">
+        <v>1.8128</v>
+      </c>
+      <c r="C313" t="n">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="s">
+        <v>766</v>
+      </c>
+      <c r="B314" t="n">
+        <v>1.82938</v>
+      </c>
+      <c r="C314" t="n">
+        <v>24.52</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="s">
+        <v>766</v>
+      </c>
+      <c r="B315" t="n">
+        <v>1.8436</v>
+      </c>
+      <c r="C315" t="n">
+        <v>24.76</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="s">
+        <v>766</v>
+      </c>
+      <c r="B316" t="n">
+        <v>1.85308</v>
+      </c>
+      <c r="C316" t="n">
+        <v>24.95</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="s">
+        <v>766</v>
+      </c>
+      <c r="B317" t="n">
+        <v>1.86967</v>
+      </c>
+      <c r="C317" t="n">
+        <v>24.34</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="s">
+        <v>766</v>
+      </c>
+      <c r="B318" t="n">
+        <v>1.87678</v>
+      </c>
+      <c r="C318" t="n">
+        <v>23.85</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="s">
+        <v>766</v>
+      </c>
+      <c r="B319" t="n">
+        <v>1.88389</v>
+      </c>
+      <c r="C319" t="n">
+        <v>23.25</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="s">
+        <v>766</v>
+      </c>
+      <c r="B320" t="n">
+        <v>1.891</v>
+      </c>
+      <c r="C320" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="s">
+        <v>766</v>
+      </c>
+      <c r="B321" t="n">
+        <v>1.89573</v>
+      </c>
+      <c r="C321" t="n">
+        <v>21.18</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="s">
+        <v>766</v>
+      </c>
+      <c r="B322" t="n">
+        <v>1.90284</v>
+      </c>
+      <c r="C322" t="n">
+        <v>19.18</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="s">
+        <v>766</v>
+      </c>
+      <c r="B323" t="n">
+        <v>1.90521</v>
+      </c>
+      <c r="C323" t="n">
+        <v>17.12</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="s">
+        <v>766</v>
+      </c>
+      <c r="B324" t="n">
+        <v>1.91943</v>
+      </c>
+      <c r="C324" t="n">
+        <v>16.02</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="s">
+        <v>766</v>
+      </c>
+      <c r="B325" t="n">
+        <v>1.92417</v>
+      </c>
+      <c r="C325" t="n">
+        <v>15.42</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="s">
+        <v>766</v>
+      </c>
+      <c r="B326" t="n">
+        <v>1.92654</v>
+      </c>
+      <c r="C326" t="n">
+        <v>15.66</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="s">
+        <v>766</v>
+      </c>
+      <c r="B327" t="n">
+        <v>1.93365</v>
+      </c>
+      <c r="C327" t="n">
+        <v>16.15</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="s">
+        <v>766</v>
+      </c>
+      <c r="B328" t="n">
+        <v>1.95261</v>
+      </c>
+      <c r="C328" t="n">
+        <v>16.69</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="s">
+        <v>766</v>
+      </c>
+      <c r="B329" t="n">
+        <v>1.95972</v>
+      </c>
+      <c r="C329" t="n">
+        <v>17.24</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="s">
+        <v>766</v>
+      </c>
+      <c r="B330" t="n">
+        <v>1.96682</v>
+      </c>
+      <c r="C330" t="n">
+        <v>17.78</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="s">
+        <v>766</v>
+      </c>
+      <c r="B331" t="n">
+        <v>1.97393</v>
+      </c>
+      <c r="C331" t="n">
+        <v>18.45</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="s">
+        <v>766</v>
+      </c>
+      <c r="B332" t="n">
+        <v>1.97867</v>
+      </c>
+      <c r="C332" t="n">
+        <v>19.36</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="s">
+        <v>766</v>
+      </c>
+      <c r="B333" t="n">
+        <v>1.98578</v>
+      </c>
+      <c r="C333" t="n">
+        <v>20.15</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="s">
+        <v>766</v>
+      </c>
+      <c r="B334" t="n">
+        <v>1.98578</v>
+      </c>
+      <c r="C334" t="n">
+        <v>20.76</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="s">
+        <v>766</v>
+      </c>
+      <c r="B335" t="n">
+        <v>1.98815</v>
+      </c>
+      <c r="C335" t="n">
+        <v>21.85</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="s">
+        <v>766</v>
+      </c>
+      <c r="B336" t="n">
+        <v>1.99526</v>
+      </c>
+      <c r="C336" t="n">
+        <v>23.07</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="s">
+        <v>766</v>
+      </c>
+      <c r="B337" t="n">
+        <v>2.00237</v>
+      </c>
+      <c r="C337" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="s">
+        <v>766</v>
+      </c>
+      <c r="B338" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="C338" t="n">
+        <v>25.55</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="s">
+        <v>766</v>
+      </c>
+      <c r="B339" t="n">
+        <v>2.00711</v>
+      </c>
+      <c r="C339" t="n">
+        <v>27.01</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="s">
+        <v>766</v>
+      </c>
+      <c r="B340" t="n">
+        <v>2.01422</v>
+      </c>
+      <c r="C340" t="n">
+        <v>27.92</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="s">
+        <v>766</v>
+      </c>
+      <c r="B341" t="n">
+        <v>2.03081</v>
+      </c>
+      <c r="C341" t="n">
+        <v>28.22</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="s">
+        <v>766</v>
+      </c>
+      <c r="B342" t="n">
+        <v>2.05687</v>
+      </c>
+      <c r="C342" t="n">
+        <v>28.59</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="s">
+        <v>766</v>
+      </c>
+      <c r="B343" t="n">
+        <v>2.06872</v>
+      </c>
+      <c r="C343" t="n">
+        <v>28.83</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="s">
+        <v>766</v>
+      </c>
+      <c r="B344" t="n">
+        <v>2.09005</v>
+      </c>
+      <c r="C344" t="n">
+        <v>29.01</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="s">
+        <v>766</v>
+      </c>
+      <c r="B345" t="n">
+        <v>2.12085</v>
+      </c>
+      <c r="C345" t="n">
+        <v>29.01</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="s">
+        <v>766</v>
+      </c>
+      <c r="B346" t="n">
+        <v>2.13981</v>
+      </c>
+      <c r="C346" t="n">
+        <v>28.59</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="s">
+        <v>766</v>
+      </c>
+      <c r="B347" t="n">
+        <v>2.15166</v>
+      </c>
+      <c r="C347" t="n">
+        <v>28.1</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="s">
+        <v>766</v>
+      </c>
+      <c r="B348" t="n">
+        <v>2.16114</v>
+      </c>
+      <c r="C348" t="n">
+        <v>27.92</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="s">
+        <v>766</v>
+      </c>
+      <c r="B349" t="n">
+        <v>2.1872</v>
+      </c>
+      <c r="C349" t="n">
+        <v>27.56</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="s">
+        <v>766</v>
+      </c>
+      <c r="B350" t="n">
+        <v>2.20853</v>
+      </c>
+      <c r="C350" t="n">
+        <v>27.44</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="s">
+        <v>766</v>
+      </c>
+      <c r="B351" t="n">
+        <v>2.23223</v>
+      </c>
+      <c r="C351" t="n">
+        <v>27.74</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="s">
+        <v>766</v>
+      </c>
+      <c r="B352" t="n">
+        <v>2.24408</v>
+      </c>
+      <c r="C352" t="n">
+        <v>28.04</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="s">
+        <v>766</v>
+      </c>
+      <c r="B353" t="n">
+        <v>2.25829</v>
+      </c>
+      <c r="C353" t="n">
+        <v>28.04</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="s">
+        <v>766</v>
+      </c>
+      <c r="B354" t="n">
+        <v>2.2654</v>
+      </c>
+      <c r="C354" t="n">
+        <v>27.92</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="s">
+        <v>766</v>
+      </c>
+      <c r="B355" t="n">
+        <v>2.27251</v>
+      </c>
+      <c r="C355" t="n">
+        <v>26.89</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="s">
+        <v>766</v>
+      </c>
+      <c r="B356" t="n">
+        <v>2.27725</v>
+      </c>
+      <c r="C356" t="n">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="s">
+        <v>766</v>
+      </c>
+      <c r="B357" t="n">
+        <v>2.27962</v>
+      </c>
+      <c r="C357" t="n">
+        <v>25.55</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="s">
+        <v>766</v>
+      </c>
+      <c r="B358" t="n">
+        <v>2.28673</v>
+      </c>
+      <c r="C358" t="n">
+        <v>24.76</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="s">
+        <v>766</v>
+      </c>
+      <c r="B359" t="n">
+        <v>2.29147</v>
+      </c>
+      <c r="C359" t="n">
+        <v>22.76</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="s">
+        <v>766</v>
+      </c>
+      <c r="B360" t="n">
+        <v>2.30095</v>
+      </c>
+      <c r="C360" t="n">
+        <v>20.82</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="s">
+        <v>766</v>
+      </c>
+      <c r="B361" t="n">
+        <v>2.30569</v>
+      </c>
+      <c r="C361" t="n">
+        <v>19.61</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="s">
+        <v>766</v>
+      </c>
+      <c r="B362" t="n">
+        <v>2.3128</v>
+      </c>
+      <c r="C362" t="n">
+        <v>18.63</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="s">
+        <v>766</v>
+      </c>
+      <c r="B363" t="n">
+        <v>2.31991</v>
+      </c>
+      <c r="C363" t="n">
+        <v>17.48</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="s">
+        <v>766</v>
+      </c>
+      <c r="B364" t="n">
+        <v>2.32938</v>
+      </c>
+      <c r="C364" t="n">
+        <v>16.51</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="s">
+        <v>766</v>
+      </c>
+      <c r="B365" t="n">
+        <v>2.34123</v>
+      </c>
+      <c r="C365" t="n">
+        <v>16.21</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="s">
+        <v>766</v>
+      </c>
+      <c r="B366" t="n">
+        <v>2.34834</v>
+      </c>
+      <c r="C366" t="n">
+        <v>17.24</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="s">
+        <v>766</v>
+      </c>
+      <c r="B367" t="n">
+        <v>2.35545</v>
+      </c>
+      <c r="C367" t="n">
+        <v>17.97</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="s">
+        <v>766</v>
+      </c>
+      <c r="B368" t="n">
+        <v>2.36967</v>
+      </c>
+      <c r="C368" t="n">
+        <v>18.33</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="s">
+        <v>766</v>
+      </c>
+      <c r="B369" t="n">
+        <v>2.38863</v>
+      </c>
+      <c r="C369" t="n">
+        <v>18.69</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="s">
+        <v>766</v>
+      </c>
+      <c r="B370" t="n">
+        <v>2.3981</v>
+      </c>
+      <c r="C370" t="n">
+        <v>19.0</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="s">
+        <v>766</v>
+      </c>
+      <c r="B371" t="n">
+        <v>2.3981</v>
+      </c>
+      <c r="C371" t="n">
+        <v>19.79</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="s">
+        <v>766</v>
+      </c>
+      <c r="B372" t="n">
+        <v>2.40284</v>
+      </c>
+      <c r="C372" t="n">
+        <v>20.39</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="s">
+        <v>766</v>
+      </c>
+      <c r="B373" t="n">
+        <v>2.40521</v>
+      </c>
+      <c r="C373" t="n">
+        <v>20.76</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="s">
+        <v>766</v>
+      </c>
+      <c r="B374" t="n">
+        <v>2.41706</v>
+      </c>
+      <c r="C374" t="n">
+        <v>21.37</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="s">
+        <v>766</v>
+      </c>
+      <c r="B375" t="n">
+        <v>2.41943</v>
+      </c>
+      <c r="C375" t="n">
+        <v>21.73</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="s">
+        <v>766</v>
+      </c>
+      <c r="B376" t="n">
+        <v>2.43365</v>
+      </c>
+      <c r="C376" t="n">
+        <v>20.76</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="s">
+        <v>766</v>
+      </c>
+      <c r="B377" t="n">
+        <v>2.43365</v>
+      </c>
+      <c r="C377" t="n">
+        <v>20.27</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="s">
+        <v>766</v>
+      </c>
+      <c r="B378" t="n">
+        <v>2.45024</v>
+      </c>
+      <c r="C378" t="n">
+        <v>19.18</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="s">
+        <v>766</v>
+      </c>
+      <c r="B379" t="n">
+        <v>2.46445</v>
+      </c>
+      <c r="C379" t="n">
+        <v>18.82</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="s">
+        <v>766</v>
+      </c>
+      <c r="B380" t="n">
+        <v>2.47867</v>
+      </c>
+      <c r="C380" t="n">
+        <v>18.69</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="s">
+        <v>766</v>
+      </c>
+      <c r="B381" t="n">
+        <v>2.47867</v>
+      </c>
+      <c r="C381" t="n">
+        <v>19.24</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="s">
+        <v>766</v>
+      </c>
+      <c r="B382" t="n">
+        <v>2.48578</v>
+      </c>
+      <c r="C382" t="n">
+        <v>19.79</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="s">
+        <v>766</v>
+      </c>
+      <c r="B383" t="n">
+        <v>2.49289</v>
+      </c>
+      <c r="C383" t="n">
+        <v>20.76</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="s">
+        <v>766</v>
+      </c>
+      <c r="B384" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C384" t="n">
+        <v>20.94</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="s">
+        <v>766</v>
+      </c>
+      <c r="B385" t="n">
+        <v>2.50237</v>
+      </c>
+      <c r="C385" t="n">
+        <v>22.09</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="s">
+        <v>766</v>
+      </c>
+      <c r="B386" t="n">
+        <v>2.50948</v>
+      </c>
+      <c r="C386" t="n">
+        <v>22.58</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="s">
+        <v>766</v>
+      </c>
+      <c r="B387" t="n">
+        <v>2.51659</v>
+      </c>
+      <c r="C387" t="n">
+        <v>23.07</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="s">
+        <v>766</v>
+      </c>
+      <c r="B388" t="n">
+        <v>2.52844</v>
+      </c>
+      <c r="C388" t="n">
+        <v>23.31</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="s">
+        <v>766</v>
+      </c>
+      <c r="B389" t="n">
+        <v>2.53791</v>
+      </c>
+      <c r="C389" t="n">
+        <v>22.28</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="s">
+        <v>766</v>
+      </c>
+      <c r="B390" t="n">
+        <v>2.54976</v>
+      </c>
+      <c r="C390" t="n">
+        <v>21.12</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="s">
+        <v>766</v>
+      </c>
+      <c r="B391" t="n">
+        <v>2.5545</v>
+      </c>
+      <c r="C391" t="n">
+        <v>20.09</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="s">
+        <v>766</v>
+      </c>
+      <c r="B392" t="n">
+        <v>2.56161</v>
+      </c>
+      <c r="C392" t="n">
+        <v>19.36</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="s">
+        <v>766</v>
+      </c>
+      <c r="B393" t="n">
+        <v>2.57109</v>
+      </c>
+      <c r="C393" t="n">
+        <v>18.27</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="s">
+        <v>766</v>
+      </c>
+      <c r="B394" t="n">
+        <v>2.58294</v>
+      </c>
+      <c r="C394" t="n">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="s">
+        <v>766</v>
+      </c>
+      <c r="B395" t="n">
+        <v>2.59242</v>
+      </c>
+      <c r="C395" t="n">
+        <v>16.87</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="s">
+        <v>766</v>
+      </c>
+      <c r="B396" t="n">
+        <v>2.61374</v>
+      </c>
+      <c r="C396" t="n">
+        <v>16.39</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="s">
+        <v>766</v>
+      </c>
+      <c r="B397" t="n">
+        <v>2.62559</v>
+      </c>
+      <c r="C397" t="n">
+        <v>16.69</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="s">
+        <v>766</v>
+      </c>
+      <c r="B398" t="n">
+        <v>2.64218</v>
+      </c>
+      <c r="C398" t="n">
+        <v>16.93</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="s">
+        <v>766</v>
+      </c>
+      <c r="B399" t="n">
+        <v>2.64692</v>
+      </c>
+      <c r="C399" t="n">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="s">
+        <v>766</v>
+      </c>
+      <c r="B400" t="n">
+        <v>2.65166</v>
+      </c>
+      <c r="C400" t="n">
+        <v>18.33</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="s">
+        <v>766</v>
+      </c>
+      <c r="B401" t="n">
+        <v>2.65403</v>
+      </c>
+      <c r="C401" t="n">
+        <v>19.24</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="s">
+        <v>766</v>
+      </c>
+      <c r="B402" t="n">
+        <v>2.66588</v>
+      </c>
+      <c r="C402" t="n">
+        <v>20.76</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="s">
+        <v>766</v>
+      </c>
+      <c r="B403" t="n">
+        <v>2.67299</v>
+      </c>
+      <c r="C403" t="n">
+        <v>22.58</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="s">
+        <v>766</v>
+      </c>
+      <c r="B404" t="n">
+        <v>2.67536</v>
+      </c>
+      <c r="C404" t="n">
+        <v>23.61</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="s">
+        <v>766</v>
+      </c>
+      <c r="B405" t="n">
+        <v>2.68009</v>
+      </c>
+      <c r="C405" t="n">
+        <v>23.98</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="s">
+        <v>766</v>
+      </c>
+      <c r="B406" t="n">
+        <v>2.68957</v>
+      </c>
+      <c r="C406" t="n">
+        <v>24.34</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="s">
+        <v>766</v>
+      </c>
+      <c r="B407" t="n">
+        <v>2.71801</v>
+      </c>
+      <c r="C407" t="n">
+        <v>25.25</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="s">
+        <v>766</v>
+      </c>
+      <c r="B408" t="n">
+        <v>2.72512</v>
+      </c>
+      <c r="C408" t="n">
+        <v>25.92</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="s">
+        <v>766</v>
+      </c>
+      <c r="B409" t="n">
+        <v>2.72512</v>
+      </c>
+      <c r="C409" t="n">
+        <v>27.44</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="s">
+        <v>766</v>
+      </c>
+      <c r="B410" t="n">
+        <v>2.73697</v>
+      </c>
+      <c r="C410" t="n">
+        <v>28.59</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="s">
+        <v>766</v>
+      </c>
+      <c r="B411" t="n">
+        <v>2.73934</v>
+      </c>
+      <c r="C411" t="n">
+        <v>30.23</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="s">
+        <v>766</v>
+      </c>
+      <c r="B412" t="n">
+        <v>2.74645</v>
+      </c>
+      <c r="C412" t="n">
+        <v>31.62</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="s">
+        <v>766</v>
+      </c>
+      <c r="B413" t="n">
+        <v>2.75118</v>
+      </c>
+      <c r="C413" t="n">
+        <v>32.23</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="s">
+        <v>766</v>
+      </c>
+      <c r="B414" t="n">
+        <v>2.75592</v>
+      </c>
+      <c r="C414" t="n">
+        <v>33.2</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="s">
+        <v>766</v>
+      </c>
+      <c r="B415" t="n">
+        <v>2.76303</v>
+      </c>
+      <c r="C415" t="n">
+        <v>33.4</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="s">
+        <v>766</v>
+      </c>
+      <c r="B416" t="n">
+        <v>2.77725</v>
+      </c>
+      <c r="C416" t="n">
+        <v>32.53</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="s">
+        <v>766</v>
+      </c>
+      <c r="B417" t="n">
+        <v>2.78673</v>
+      </c>
+      <c r="C417" t="n">
+        <v>31.62</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="s">
+        <v>766</v>
+      </c>
+      <c r="B418" t="n">
+        <v>2.79147</v>
+      </c>
+      <c r="C418" t="n">
+        <v>30.71</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="s">
+        <v>766</v>
+      </c>
+      <c r="B419" t="n">
+        <v>2.79384</v>
+      </c>
+      <c r="C419" t="n">
+        <v>30.11</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="s">
+        <v>766</v>
+      </c>
+      <c r="B420" t="n">
+        <v>2.80569</v>
+      </c>
+      <c r="C420" t="n">
+        <v>29.86</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="s">
+        <v>766</v>
+      </c>
+      <c r="B421" t="n">
+        <v>2.82701</v>
+      </c>
+      <c r="C421" t="n">
+        <v>29.68</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="s">
+        <v>766</v>
+      </c>
+      <c r="B422" t="n">
+        <v>2.85308</v>
+      </c>
+      <c r="C422" t="n">
+        <v>29.32</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="s">
+        <v>766</v>
+      </c>
+      <c r="B423" t="n">
+        <v>2.86256</v>
+      </c>
+      <c r="C423" t="n">
+        <v>28.04</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="s">
+        <v>766</v>
+      </c>
+      <c r="B424" t="n">
+        <v>2.86967</v>
+      </c>
+      <c r="C424" t="n">
+        <v>27.01</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="s">
+        <v>766</v>
+      </c>
+      <c r="B425" t="n">
+        <v>2.87678</v>
+      </c>
+      <c r="C425" t="n">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="s">
+        <v>766</v>
+      </c>
+      <c r="B426" t="n">
+        <v>2.88389</v>
+      </c>
+      <c r="C426" t="n">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="s">
+        <v>766</v>
+      </c>
+      <c r="B427" t="n">
+        <v>2.89573</v>
+      </c>
+      <c r="C427" t="n">
+        <v>23.79</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="s">
+        <v>766</v>
+      </c>
+      <c r="B428" t="n">
+        <v>2.90284</v>
+      </c>
+      <c r="C428" t="n">
+        <v>22.94</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="s">
+        <v>766</v>
+      </c>
+      <c r="B429" t="n">
+        <v>2.90995</v>
+      </c>
+      <c r="C429" t="n">
+        <v>23.79</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="s">
+        <v>766</v>
+      </c>
+      <c r="B430" t="n">
+        <v>2.91232</v>
+      </c>
+      <c r="C430" t="n">
+        <v>24.58</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="s">
+        <v>766</v>
+      </c>
+      <c r="B431" t="n">
+        <v>2.92417</v>
+      </c>
+      <c r="C431" t="n">
+        <v>25.13</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="s">
+        <v>766</v>
+      </c>
+      <c r="B432" t="n">
+        <v>2.93128</v>
+      </c>
+      <c r="C432" t="n">
+        <v>26.28</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="s">
+        <v>766</v>
+      </c>
+      <c r="B433" t="n">
+        <v>2.93128</v>
+      </c>
+      <c r="C433" t="n">
+        <v>27.62</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="s">
+        <v>766</v>
+      </c>
+      <c r="B434" t="n">
+        <v>2.93839</v>
+      </c>
+      <c r="C434" t="n">
+        <v>28.65</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="s">
+        <v>766</v>
+      </c>
+      <c r="B435" t="n">
+        <v>2.9455</v>
+      </c>
+      <c r="C435" t="n">
+        <v>30.23</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="s">
+        <v>766</v>
+      </c>
+      <c r="B436" t="n">
+        <v>2.95261</v>
+      </c>
+      <c r="C436" t="n">
+        <v>31.26</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="s">
+        <v>766</v>
+      </c>
+      <c r="B437" t="n">
+        <v>2.95261</v>
+      </c>
+      <c r="C437" t="n">
+        <v>31.68</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="s">
+        <v>766</v>
+      </c>
+      <c r="B438" t="n">
+        <v>2.95972</v>
+      </c>
+      <c r="C438" t="n">
+        <v>32.41</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="s">
+        <v>766</v>
+      </c>
+      <c r="B439" t="n">
+        <v>2.99289</v>
+      </c>
+      <c r="C439" t="n">
+        <v>32.23</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="s">
+        <v>766</v>
+      </c>
+      <c r="B440" t="n">
+        <v>3.04265</v>
+      </c>
+      <c r="C440" t="n">
+        <v>31.87</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="s">
+        <v>766</v>
+      </c>
+      <c r="B441" t="n">
+        <v>3.07109</v>
+      </c>
+      <c r="C441" t="n">
+        <v>31.62</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="s">
+        <v>766</v>
+      </c>
+      <c r="B442" t="n">
+        <v>3.09005</v>
+      </c>
+      <c r="C442" t="n">
+        <v>30.96</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="s">
+        <v>766</v>
+      </c>
+      <c r="B443" t="n">
+        <v>3.11137</v>
+      </c>
+      <c r="C443" t="n">
+        <v>30.41</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="s">
+        <v>766</v>
+      </c>
+      <c r="B444" t="n">
+        <v>3.13981</v>
+      </c>
+      <c r="C444" t="n">
+        <v>29.74</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="s">
+        <v>766</v>
+      </c>
+      <c r="B445" t="n">
+        <v>3.14692</v>
+      </c>
+      <c r="C445" t="n">
+        <v>30.23</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="s">
+        <v>766</v>
+      </c>
+      <c r="B446" t="n">
+        <v>3.16114</v>
+      </c>
+      <c r="C446" t="n">
+        <v>30.71</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="s">
+        <v>766</v>
+      </c>
+      <c r="B447" t="n">
+        <v>3.18009</v>
+      </c>
+      <c r="C447" t="n">
+        <v>31.32</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="s">
+        <v>766</v>
+      </c>
+      <c r="B448" t="n">
+        <v>3.18246</v>
+      </c>
+      <c r="C448" t="n">
+        <v>31.62</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="s">
+        <v>766</v>
+      </c>
+      <c r="B449" t="n">
+        <v>3.19668</v>
+      </c>
+      <c r="C449" t="n">
+        <v>32.05</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="s">
+        <v>766</v>
+      </c>
+      <c r="B450" t="n">
+        <v>3.20853</v>
+      </c>
+      <c r="C450" t="n">
+        <v>31.08</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="s">
+        <v>766</v>
+      </c>
+      <c r="B451" t="n">
+        <v>3.22275</v>
+      </c>
+      <c r="C451" t="n">
+        <v>30.41</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="s">
+        <v>766</v>
+      </c>
+      <c r="B452" t="n">
+        <v>3.22986</v>
+      </c>
+      <c r="C452" t="n">
+        <v>29.56</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="s">
+        <v>766</v>
+      </c>
+      <c r="B453" t="n">
+        <v>3.23934</v>
+      </c>
+      <c r="C453" t="n">
+        <v>28.65</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="s">
+        <v>766</v>
+      </c>
+      <c r="B454" t="n">
+        <v>3.24882</v>
+      </c>
+      <c r="C454" t="n">
+        <v>27.74</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="s">
+        <v>766</v>
+      </c>
+      <c r="B455" t="n">
+        <v>3.2654</v>
+      </c>
+      <c r="C455" t="n">
+        <v>27.74</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="s">
+        <v>766</v>
+      </c>
+      <c r="B456" t="n">
+        <v>3.27962</v>
+      </c>
+      <c r="C456" t="n">
+        <v>28.29</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="s">
+        <v>766</v>
+      </c>
+      <c r="B457" t="n">
+        <v>3.29384</v>
+      </c>
+      <c r="C457" t="n">
+        <v>28.65</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="s">
+        <v>766</v>
+      </c>
+      <c r="B458" t="n">
+        <v>3.30806</v>
+      </c>
+      <c r="C458" t="n">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="s">
+        <v>766</v>
+      </c>
+      <c r="B459" t="n">
+        <v>3.32227</v>
+      </c>
+      <c r="C459" t="n">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="s">
+        <v>766</v>
+      </c>
+      <c r="B460" t="n">
+        <v>3.34123</v>
+      </c>
+      <c r="C460" t="n">
+        <v>28.65</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="s">
+        <v>766</v>
+      </c>
+      <c r="B461" t="n">
+        <v>3.34834</v>
+      </c>
+      <c r="C461" t="n">
+        <v>28.22</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="s">
+        <v>766</v>
+      </c>
+      <c r="B462" t="n">
+        <v>3.36019</v>
+      </c>
+      <c r="C462" t="n">
+        <v>28.04</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="s">
+        <v>766</v>
+      </c>
+      <c r="B463" t="n">
+        <v>3.37441</v>
+      </c>
+      <c r="C463" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="s">
+        <v>766</v>
+      </c>
+      <c r="B464" t="n">
+        <v>3.3981</v>
+      </c>
+      <c r="C464" t="n">
+        <v>28.04</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="s">
+        <v>766</v>
+      </c>
+      <c r="B465" t="n">
+        <v>3.40284</v>
+      </c>
+      <c r="C465" t="n">
+        <v>27.56</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="s">
+        <v>766</v>
+      </c>
+      <c r="B466" t="n">
+        <v>3.40995</v>
+      </c>
+      <c r="C466" t="n">
+        <v>27.01</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="s">
+        <v>766</v>
+      </c>
+      <c r="B467" t="n">
+        <v>3.41706</v>
+      </c>
+      <c r="C467" t="n">
+        <v>26.46</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="s">
+        <v>766</v>
+      </c>
+      <c r="B468" t="n">
+        <v>3.41706</v>
+      </c>
+      <c r="C468" t="n">
+        <v>25.98</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="s">
+        <v>766</v>
+      </c>
+      <c r="B469" t="n">
+        <v>3.41943</v>
+      </c>
+      <c r="C469" t="n">
+        <v>25.37</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="s">
+        <v>766</v>
+      </c>
+      <c r="B470" t="n">
+        <v>3.42417</v>
+      </c>
+      <c r="C470" t="n">
+        <v>24.89</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="s">
+        <v>766</v>
+      </c>
+      <c r="B471" t="n">
+        <v>3.42417</v>
+      </c>
+      <c r="C471" t="n">
+        <v>24.52</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
@@ -13254,4 +19124,744 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>690</v>
+      </c>
+      <c r="B1" t="s">
+        <v>691</v>
+      </c>
+      <c r="C1" t="s">
+        <v>692</v>
+      </c>
+      <c r="D1" t="s">
+        <v>693</v>
+      </c>
+      <c r="E1" t="s">
+        <v>694</v>
+      </c>
+      <c r="F1" t="s">
+        <v>695</v>
+      </c>
+      <c r="G1" t="s">
+        <v>696</v>
+      </c>
+      <c r="H1" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>698</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-0.156552</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.157641</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.13372</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.118784</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.107827</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-0.115015</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-0.111535</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>699</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-0.160682</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.151594</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.133447</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.11829</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-0.109462</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-0.115178</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.104946</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>700</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-0.163245</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.158767</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.13476</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.12592</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.110273</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0.133065</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.177351</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>701</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-0.154155</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.153406</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.128324</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.116277</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.109605</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.120315</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.141608</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>702</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-0.155279</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.152387</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.129086</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.097013</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.106082</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.113019</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.109647</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>703</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-0.155816</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.147797</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.129697</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.103885</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.109148</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.135427</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.150318</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>704</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-0.15789</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.152711</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.131631</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.109377</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.112902</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.136058</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.144495</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>705</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-0.154481</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.151307</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.129787</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.123195</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.108498</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.113131</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.135996</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>706</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.162295</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.161631</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.132712</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.118482</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.106981</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.116747</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.13248</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>690</v>
+      </c>
+      <c r="B1" t="s">
+        <v>691</v>
+      </c>
+      <c r="C1" t="s">
+        <v>692</v>
+      </c>
+      <c r="D1" t="s">
+        <v>693</v>
+      </c>
+      <c r="E1" t="s">
+        <v>694</v>
+      </c>
+      <c r="F1" t="s">
+        <v>707</v>
+      </c>
+      <c r="G1" t="s">
+        <v>708</v>
+      </c>
+      <c r="H1" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>710</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-0.146156</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.140679</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.111752</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.107426</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.110803</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-0.103561</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-0.096953</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>711</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-0.136016</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.13871</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.106671</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.073596</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-0.099984</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-0.093179</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.08035</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>712</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-0.153385</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.143999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.122427</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.086949</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.114312</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0.107412</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.101239</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>713</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-0.163138</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.146945</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.140853</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.088211</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.128195</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.123156</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.119236</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>714</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-0.16251</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.154175</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.14409</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.104657</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.125703</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.121595</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>715</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-0.143053</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.132804</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.10909</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.107683</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.115739</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.101123</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.102833</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>716</v>
+      </c>
+      <c r="B1" t="s">
+        <v>717</v>
+      </c>
+      <c r="C1" t="s">
+        <v>718</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>719</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3.399</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.166122</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>720</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3.105</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.158627</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>721</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.69</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2.987</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.175551</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>722</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.149787</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>723</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.124842</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>724</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.503</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.124629</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>725</v>
+      </c>
+      <c r="B1" t="s">
+        <v>717</v>
+      </c>
+      <c r="C1" t="s">
+        <v>718</v>
+      </c>
+      <c r="D1" t="s">
+        <v>726</v>
+      </c>
+      <c r="E1" t="s">
+        <v>727</v>
+      </c>
+      <c r="F1" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>729</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2.784</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.165769</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.189094</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.136118</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>730</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.170581</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.18713</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-0.13037</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>731</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.974</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.148997</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.166529</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.145055</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>732</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.757</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.137649</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.155573</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.146628</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>733</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1.346</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.128351</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.129297</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.137781</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>734</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.135168</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.129104</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.146199</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>735</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.026</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.134686</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.143766</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.147553</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>